--- a/dados/validacao/rotulagem_arthur.xlsx
+++ b/dados/validacao/rotulagem_arthur.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="instrucoes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="repositorios" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="releases" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="instrucoes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="repositorios" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="releases" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -445,9 +445,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -462,9 +459,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -485,9 +479,6 @@
           <t xml:space="preserve">  entregas_reais: as releases do repositório representam entregas reais ao usuário? sim, não ou incerto.</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -611,6 +602,16 @@
           <t>https://github.com/AsyncHttpClient/async-http-client</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -623,6 +624,16 @@
           <t>https://github.com/Bitterbot-AI/bitterbot-desktop</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -635,6 +646,21 @@
           <t>https://github.com/Brooooooklyn/canvas</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Tags skia-* são só build.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -647,6 +673,16 @@
           <t>https://github.com/EmbarkStudios/cargo-deny</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -659,6 +695,21 @@
           <t>https://github.com/IfcOpenShell/IfcOpenShell</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>São builds diários automáticos.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -671,6 +722,16 @@
           <t>https://github.com/ItzCrazyKns/Vane</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -683,6 +744,16 @@
           <t>https://github.com/Legcord/Legcord</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -695,6 +766,16 @@
           <t>https://github.com/OpenBMB/StaffDeck</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -707,6 +788,16 @@
           <t>https://github.com/PCSX2/pcsx2</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -719,6 +810,16 @@
           <t>https://github.com/RongleCat/grok-app</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -731,6 +832,16 @@
           <t>https://github.com/VoltAgent/voltagent</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -743,6 +854,16 @@
           <t>https://github.com/YishenTu/claudian</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -755,6 +876,16 @@
           <t>https://github.com/aeron-io/aeron</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -767,6 +898,16 @@
           <t>https://github.com/apache/pulsar</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -779,6 +920,16 @@
           <t>https://github.com/assistant-ui/assistant-ui</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -791,6 +942,16 @@
           <t>https://github.com/aws-actions/amazon-ecr-login</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -803,6 +964,16 @@
           <t>https://github.com/ayangweb/BongoCat</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -815,6 +986,16 @@
           <t>https://github.com/benoitc/hackney</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -827,6 +1008,16 @@
           <t>https://github.com/cinnyapp/cinny</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -839,6 +1030,16 @@
           <t>https://github.com/cloud-in-a-bottle/cloud-in-a-bottle</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -851,6 +1052,21 @@
           <t>https://github.com/cloudflare/mcp-server-cloudflare</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>incerto</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Releases de pacotes internos.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -863,6 +1079,16 @@
           <t>https://github.com/community-shaders/skyrim-community-shaders</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -875,6 +1101,16 @@
           <t>https://github.com/directus/directus</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -887,6 +1123,16 @@
           <t>https://github.com/dotnet/efcore</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -899,6 +1145,16 @@
           <t>https://github.com/dotnetcore/BootstrapBlazor</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -911,6 +1167,21 @@
           <t>https://github.com/dynamoose/dynamoose</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Várias republicações por erro no publish.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -923,6 +1194,16 @@
           <t>https://github.com/ergebnis/composer-normalize</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -935,6 +1216,21 @@
           <t>https://github.com/hexclave/hexclave</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>incerto</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Builds do dashboard, não do produto.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -947,6 +1243,16 @@
           <t>https://github.com/infinispan/infinispan</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -959,6 +1265,16 @@
           <t>https://github.com/itchio/itch</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -971,6 +1287,16 @@
           <t>https://github.com/jolicode/JoliNotif</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -983,6 +1309,16 @@
           <t>https://github.com/krille-chan/fluffychat</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -995,6 +1331,21 @@
           <t>https://github.com/kubeai-project/kubeai</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Tags helm-chart-* são empacotamento.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1007,6 +1358,16 @@
           <t>https://github.com/ludo-technologies/pyscn</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1019,6 +1380,16 @@
           <t>https://github.com/meta-pytorch/botorch</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1031,6 +1402,16 @@
           <t>https://github.com/microsoft/qdk</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1043,6 +1424,16 @@
           <t>https://github.com/mullvad/mullvadvpn-app</t>
         </is>
       </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1055,6 +1446,16 @@
           <t>https://github.com/nilsteampassnet/TeamPass</t>
         </is>
       </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1067,6 +1468,16 @@
           <t>https://github.com/ohler55/oj</t>
         </is>
       </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1079,6 +1490,16 @@
           <t>https://github.com/openmm/openmm</t>
         </is>
       </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1091,6 +1512,16 @@
           <t>https://github.com/pH7Software/pH7-Social-Dating-CMS</t>
         </is>
       </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1103,6 +1534,16 @@
           <t>https://github.com/pgrundev/pgbot</t>
         </is>
       </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1115,6 +1556,16 @@
           <t>https://github.com/plasma-umass/scalene</t>
         </is>
       </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1127,6 +1578,16 @@
           <t>https://github.com/qiutongxue/oba-live-tool</t>
         </is>
       </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1139,6 +1600,16 @@
           <t>https://github.com/rachelos/we-mp-rss</t>
         </is>
       </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1151,6 +1622,16 @@
           <t>https://github.com/raphaelmansuy/edgequake</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1163,6 +1644,16 @@
           <t>https://github.com/react-cosmos/react-cosmos</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1175,6 +1666,16 @@
           <t>https://github.com/remeda/remeda</t>
         </is>
       </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1187,6 +1688,16 @@
           <t>https://github.com/run-llama/liteparse</t>
         </is>
       </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1199,6 +1710,16 @@
           <t>https://github.com/runfinch/finch</t>
         </is>
       </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1211,6 +1732,16 @@
           <t>https://github.com/sass/dart-sass</t>
         </is>
       </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ferramenta CLI</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1223,6 +1754,16 @@
           <t>https://github.com/softprops/action-gh-release</t>
         </is>
       </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1235,6 +1776,16 @@
           <t>https://github.com/softwaremill/sttp</t>
         </is>
       </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1247,6 +1798,16 @@
           <t>https://github.com/tailwindlabs/prettier-plugin-tailwindcss</t>
         </is>
       </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1259,6 +1820,16 @@
           <t>https://github.com/ustctug/ustcthesis</t>
         </is>
       </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>outro</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1271,6 +1842,16 @@
           <t>https://github.com/vicanso/zedis</t>
         </is>
       </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1283,6 +1864,16 @@
           <t>https://github.com/vue-stripe/vue-stripe</t>
         </is>
       </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>biblioteca/framework</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1295,6 +1886,16 @@
           <t>https://github.com/wk42worldworld/cybercode</t>
         </is>
       </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1307,6 +1908,16 @@
           <t>https://github.com/zereight/gitlab-mcp</t>
         </is>
       </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1317,6 +1928,16 @@
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>https://github.com/zhblue/hustoj</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>aplicação/serviço</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
     </row>
@@ -1489,6 +2110,11 @@
           <t>2025-11-14T21:20:26+00:00</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -1541,6 +2167,11 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>2026-04-12T02:53:53+00:00</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -1597,6 +2228,11 @@
       <c r="D4" t="inlineStr">
         <is>
           <t>2026-06-14T22:25:19+00:00</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -1647,6 +2283,11 @@
           <t>https://github.com/AsyncHttpClient/async-http-client/compare/async-http-client-project-2.15.0...async-http-client-project-3.0.11</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Anterior de outra linha de versão; julguei pelas notas.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1667,6 +2308,11 @@
       <c r="D5" t="inlineStr">
         <is>
           <t>2026-08-09T20:17:56+00:00</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -1717,6 +2363,11 @@
           <t>https://github.com/AsyncHttpClient/async-http-client/compare/async-http-client-project-2.16.0...async-http-client-project-3.0.12</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Anterior de outra linha de versão; julguei pelas notas.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1737,6 +2388,11 @@
       <c r="D6" t="inlineStr">
         <is>
           <t>2026-08-09T23:12:58+00:00</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -1785,6 +2441,11 @@
           <t>https://github.com/AsyncHttpClient/async-http-client/compare/async-http-client-project-3.0.13...async-http-client-project-2.16.1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Anterior de outra linha de versão; julguei pelas notas.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1800,6 +2461,11 @@
       <c r="D7" t="inlineStr">
         <is>
           <t>2026-04-12T16:47:09+00:00</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -1819,6 +2485,11 @@
           <t>https://github.com/Bitterbot-AI/bitterbot-desktop/releases/tag/orchestrator-v0.1.0</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Primeira release.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1839,6 +2510,11 @@
       <c r="D8" t="inlineStr">
         <is>
           <t>2026-08-14T16:48:05+00:00</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -1905,6 +2581,11 @@
           <t>2026-08-14T17:11:47+00:00</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Prebuilt `bitterbot-orchestrator` v0.2.1 binaries.
@@ -1948,6 +2629,11 @@
       <c r="D10" t="inlineStr">
         <is>
           <t>2026-08-28T13:43:10+00:00</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -2019,6 +2705,11 @@
           <t>2026-09-23T13:43:33+00:00</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
           <t>## [1.1.0](https://github.com/Bitterbot-AI/bitterbot-desktop/compare/v1.0.0...v1.1.0) (2026-09-22)
@@ -2088,6 +2779,11 @@
           <t>2025-11-27T14:19:42+00:00</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -2136,6 +2832,11 @@
           <t>2026-02-09T14:38:08+00:00</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -2181,6 +2882,11 @@
       <c r="D14" t="inlineStr">
         <is>
           <t>2026-07-28T07:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -2236,6 +2942,11 @@
           <t>2026-08-13T14:34:31+00:00</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -2279,6 +2990,11 @@
       <c r="D16" t="inlineStr">
         <is>
           <t>2026-09-09T08:32:49+00:00</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -2307,6 +3023,11 @@
           <t>https://github.com/Brooooooklyn/canvas/compare/v1.0.8...skia-a9c42c9f</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tag de build, sem notas.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2327,6 +3048,11 @@
       <c r="D17" t="inlineStr">
         <is>
           <t>2025-11-24T10:21:33+00:00</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -2380,6 +3106,11 @@
       <c r="D18" t="inlineStr">
         <is>
           <t>2026-04-10T11:06:13+00:00</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -2441,6 +3172,11 @@
           <t>2026-05-11T10:50:29+00:00</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
           <t>### Fixed
@@ -2486,6 +3222,11 @@
           <t>2026-05-28T08:13:27+00:00</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
           <t>### Fixed
@@ -2529,6 +3270,11 @@
       <c r="D21" t="inlineStr">
         <is>
           <t>2026-06-15T14:28:33+00:00</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -2582,6 +3328,11 @@
           <t>2026-01-21T07:57:47+00:00</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
           <t>See README in https://github.com/IfcOpenShell/bonsai_unstable_repo/ on how to setup autoupdates for daily Bonsai builds.</t>
@@ -2600,6 +3351,11 @@
       <c r="I22" s="2" t="inlineStr">
         <is>
           <t>https://github.com/IfcOpenShell/IfcOpenShell/compare/bonsai-0.8.5-alpha2601210717...bonsai-0.8.5-alpha2601210754</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Revert de mudança recente.</t>
         </is>
       </c>
     </row>
@@ -2624,6 +3380,11 @@
           <t>2026-04-05T21:47:00+00:00</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
           <t>See README in https://github.com/IfcOpenShell/bonsai_unstable_repo/ on how to setup autoupdates for daily Bonsai builds.</t>
@@ -2666,6 +3427,11 @@
           <t>2026-07-19T18:19:49+00:00</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
           <t>See README in https://github.com/IfcOpenShell/bonsai_unstable_repo/ on how to setup autoupdates for daily Bonsai builds.</t>
@@ -2708,6 +3474,11 @@
           <t>2026-07-25T04:01:48+00:00</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
           <t>See README in https://github.com/IfcOpenShell/bonsai_unstable_repo/ on how to setup autoupdates for daily Bonsai builds.</t>
@@ -2748,6 +3519,11 @@
       <c r="D26" t="inlineStr">
         <is>
           <t>2026-08-25T14:16:34+00:00</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -2795,6 +3571,11 @@
       <c r="D27" t="inlineStr">
         <is>
           <t>2025-10-21T10:29:37+00:00</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -2871,6 +3652,11 @@
           <t>2025-10-23T15:37:03+00:00</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
           <t># v1.11.1
@@ -2921,6 +3707,11 @@
           <t>2025-10-25T05:42:58+00:00</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
           <t># 1.11.2
@@ -2971,6 +3762,11 @@
       <c r="D30" t="inlineStr">
         <is>
           <t>2025-12-31T07:36:13+00:00</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -3025,6 +3821,11 @@
       <c r="D31" t="inlineStr">
         <is>
           <t>2026-04-10T13:30:52+00:00</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -3102,6 +3903,11 @@
           <t>2025-11-05T12:25:07+00:00</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
           <t>## What’s New in Legcord v1.1.6 🚀
@@ -3181,6 +3987,11 @@
           <t>2026-01-29T19:52:26+00:00</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
           <t>## What’s New in Legcord v1.2.0 ✨
@@ -3260,6 +4071,11 @@
           <t>2026-01-30T14:31:16+00:00</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
           <t>## What’s New in Legcord v1.2.1 ✨
@@ -3307,6 +4123,11 @@
       <c r="D35" t="inlineStr">
         <is>
           <t>2026-04-15T17:02:11+00:00</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -3385,6 +4206,11 @@
           <t>2026-04-15T18:54:58+00:00</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
           <t>## What’s New in Legcord v1.2.4 ✨
@@ -3421,6 +4247,11 @@
           <t>https://github.com/Legcord/Legcord/compare/v1.2.3...v1.2.4</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Notas repetidas da versão anterior.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3438,6 +4269,11 @@
           <t>2026-07-16T06:56:10+00:00</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
           <t>(release sem notas)</t>
@@ -3473,6 +4309,11 @@
       <c r="D38" t="inlineStr">
         <is>
           <t>2026-08-06T03:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -3537,6 +4378,11 @@
           <t>2026-08-07T03:35:41+00:00</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
           <t>(release sem notas)</t>
@@ -3581,6 +4427,11 @@
           <t>2026-08-18T09:02:35+00:00</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
           <t>(release sem notas)</t>
@@ -3599,6 +4450,11 @@
       <c r="I40" s="2" t="inlineStr">
         <is>
           <t>https://github.com/OpenBMB/StaffDeck/compare/v0.4.1-beta1...v0.4.1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Sem commits novos.</t>
         </is>
       </c>
     </row>
@@ -3623,6 +4479,11 @@
           <t>2026-09-10T07:58:01+00:00</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
           <t>(release sem notas)</t>
@@ -3663,6 +4524,11 @@
       <c r="D42" t="inlineStr">
         <is>
           <t>2026-01-04T19:50:17+00:00</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -3727,6 +4593,11 @@
           <t>2026-01-05T23:46:12+00:00</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
           <t>- [GameDB: CMR 2005 Fixes](https://github.com/PCSX2/pcsx2/pull/13782)</t>
@@ -3769,6 +4640,11 @@
           <t>2026-01-11T21:22:44+00:00</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
           <t>- Debugger: Properly reset the breakpoint skip first when skipped</t>
@@ -3809,6 +4685,11 @@
       <c r="D45" t="inlineStr">
         <is>
           <t>2026-08-28T22:47:42+00:00</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -3874,6 +4755,11 @@
           <t>2026-08-30T22:36:36+00:00</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
           <t>(release sem notas)</t>
@@ -3892,6 +4778,11 @@
       <c r="I46" s="2" t="inlineStr">
         <is>
           <t>https://github.com/PCSX2/pcsx2/compare/v2.8.0...v2.8.1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Sem notas.</t>
         </is>
       </c>
     </row>
@@ -3914,6 +4805,11 @@
       <c r="D47" t="inlineStr">
         <is>
           <t>2026-08-11T18:01:42+00:00</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -3980,6 +4876,11 @@
       <c r="D48" t="inlineStr">
         <is>
           <t>2026-08-13T18:40:09+00:00</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -4048,6 +4949,11 @@
           <t>2026-08-14T16:19:00+00:00</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
           <t># Grok App v0.2.18
@@ -4102,6 +5008,11 @@
       <c r="D50" t="inlineStr">
         <is>
           <t>2026-09-04T15:47:43+00:00</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -4187,6 +5098,11 @@
           <t>2026-09-09T15:38:41+00:00</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
           <t># Grok App v0.2.34
@@ -4262,6 +5178,11 @@
           <t>2025-10-21T16:59:43+00:00</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
           <t>### Patch Changes
@@ -4317,6 +5238,11 @@
           <t>2025-12-01T20:48:18+00:00</t>
         </is>
       </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
           <t>### Patch Changes
@@ -4359,6 +5285,11 @@
       <c r="D54" t="inlineStr">
         <is>
           <t>2025-12-09T18:16:32+00:00</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -4430,6 +5361,11 @@
           <t>2025-12-10T17:12:47+00:00</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
           <t>### Patch Changes
@@ -4479,6 +5415,11 @@
           <t>2026-02-08T21:39:40+00:00</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
           <t>### Patch Changes
@@ -4515,6 +5456,11 @@
       <c r="D57" t="inlineStr">
         <is>
           <t>2026-02-03T02:24:17+00:00</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -4574,6 +5520,11 @@
           <t>2026-03-24T01:57:23+00:00</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -4625,6 +5576,11 @@
       <c r="D59" t="inlineStr">
         <is>
           <t>2026-04-28T00:23:16+00:00</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -4677,6 +5633,11 @@
           <t>2026-08-01T20:12:00+00:00</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -4732,6 +5693,11 @@
       <c r="D61" t="inlineStr">
         <is>
           <t>2026-09-18T07:17:29+00:00</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -4813,6 +5779,11 @@
           <t>2025-10-03T11:57:50+00:00</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
           <t>### New &amp; Noteworthy
@@ -4885,6 +5856,11 @@
           <t>2026-02-05T17:31:12+00:00</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
           <t>###  Changelog
@@ -4936,6 +5912,11 @@
       <c r="D64" t="inlineStr">
         <is>
           <t>2026-03-20T14:40:46+00:00</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -5000,6 +5981,11 @@
           <t>2026-07-03T16:56:55+00:00</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
           <t>See [1.52.0 release notes](https://github.com/aeron-io/aeron/blob/master/CHANGELOG.adoc#1520-2026-07-03).</t>
@@ -5062,6 +6048,11 @@
           <t>2026-09-24T15:24:41+00:00</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
           <t>See [1.50.7 release notes](https://github.com/aeron-io/aeron/blob/master/CHANGELOG.adoc#1507-2026-09-24).</t>
@@ -5104,6 +6095,11 @@
       <c r="D67" t="inlineStr">
         <is>
           <t>2025-11-17T07:57:45+00:00</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -5157,6 +6153,11 @@
           <t>https://github.com/apache/pulsar/compare/v4.1.1...v3.0.15</t>
         </is>
       </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Anterior de outra linha de versão; julguei pelas notas.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5177,6 +6178,11 @@
       <c r="D68" t="inlineStr">
         <is>
           <t>2025-11-17T07:58:06+00:00</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -5229,6 +6235,11 @@
           <t>https://github.com/apache/pulsar/compare/v3.0.15...v4.0.8</t>
         </is>
       </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Anterior de outra linha de versão; julguei pelas notas.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5249,6 +6260,11 @@
       <c r="D69" t="inlineStr">
         <is>
           <t>2026-02-19T19:48:49+00:00</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -5301,6 +6317,11 @@
           <t>https://github.com/apache/pulsar/compare/v4.0.9...v4.1.3</t>
         </is>
       </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Anterior de outra linha de versão; julguei pelas notas.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5321,6 +6342,11 @@
       <c r="D70" t="inlineStr">
         <is>
           <t>2026-07-06T08:46:50+00:00</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
@@ -5373,6 +6399,11 @@
           <t>https://github.com/apache/pulsar/compare/v4.0.12...v4.2.3</t>
         </is>
       </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Anterior de outra linha de versão; julguei pelas notas.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5393,6 +6424,11 @@
       <c r="D71" t="inlineStr">
         <is>
           <t>2026-08-03T09:19:06+00:00</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -5446,6 +6482,11 @@
           <t>https://github.com/apache/pulsar/compare/v4.2.3...v4.0.13</t>
         </is>
       </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Anterior de outra linha de versão; julguei pelas notas.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5466,6 +6507,11 @@
       <c r="D72" t="inlineStr">
         <is>
           <t>2026-04-02T22:15:55+00:00</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
@@ -5522,6 +6568,11 @@
           <t>2026-06-12T02:29:09+00:00</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
           <t>### Patch Changes
@@ -5567,6 +6618,11 @@
           <t>2026-06-12T02:29:21+00:00</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
           <t>### Patch Changes
@@ -5590,6 +6646,11 @@
           <t>https://github.com/assistant-ui/assistant-ui/compare/%40assistant-ui%2Freact-o11y%400.0.21...%40assistant-ui%2Freact-ai-sdk%401.3.35</t>
         </is>
       </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Diz 'fix', mas é melhoria.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5612,6 +6673,11 @@
           <t>2026-09-03T14:25:19+00:00</t>
         </is>
       </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
           <t>### Patch Changes
@@ -5653,6 +6719,11 @@
       <c r="D76" t="inlineStr">
         <is>
           <t>2026-09-18T15:14:19+00:00</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -5697,6 +6768,11 @@
       <c r="D77" t="inlineStr">
         <is>
           <t>2026-03-13T21:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -5761,6 +6837,11 @@
           <t>2026-03-18T23:02:25+00:00</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
           <t>See the [changelog](CHANGELOG.md) for details about the changes included in this release.</t>
@@ -5805,6 +6886,11 @@
       <c r="D79" t="inlineStr">
         <is>
           <t>2026-04-15T21:30:25+00:00</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -5858,6 +6944,11 @@
       <c r="D80" t="inlineStr">
         <is>
           <t>2026-05-06T20:33:25+00:00</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
@@ -5912,6 +7003,11 @@
       <c r="D81" t="inlineStr">
         <is>
           <t>2026-06-12T23:35:44+00:00</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -5976,6 +7072,11 @@
           <t>2025-11-24T14:01:33+00:00</t>
         </is>
       </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
           <t>### &amp;nbsp;&amp;nbsp;&amp;nbsp;🚀 Features
@@ -6026,6 +7127,11 @@
           <t>2025-12-24T10:08:49+00:00</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
           <t>### &amp;nbsp;&amp;nbsp;&amp;nbsp;🚀 Features
@@ -6076,6 +7182,11 @@
       <c r="D84" t="inlineStr">
         <is>
           <t>2026-04-08T14:23:04+00:00</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
@@ -6134,6 +7245,11 @@
       <c r="D85" t="inlineStr">
         <is>
           <t>2026-09-28T19:35:20+00:00</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -6211,6 +7327,11 @@
       <c r="D86" t="inlineStr">
         <is>
           <t>2026-09-29T12:13:07+00:00</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
@@ -6281,6 +7402,11 @@
           <t>2026-02-21T02:21:56+00:00</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
           <t>### Dependencies
@@ -6323,6 +7449,11 @@
       <c r="D88" t="inlineStr">
         <is>
           <t>2026-06-05T09:39:46+00:00</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -6373,6 +7504,11 @@
           <t>2026-07-17T09:38:07+00:00</t>
         </is>
       </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
           <t>Bump `quic` to 1.7.1. A clean QUIC connection close (idle pooled HTTP/3 connections, orderly shutdown) no longer emits ERROR and CRASH reports from `quic_h3_connection` nor propagates an abnormal exit to the connection owner. This also removes the intermittent eunit group cancellation in the h3/wt test suites.
@@ -6416,6 +7552,11 @@
       <c r="D90" t="inlineStr">
         <is>
           <t>2026-09-24T08:14:15+00:00</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -6474,6 +7615,11 @@
           <t>https://github.com/benoitc/hackney/compare/4.7.4...4.8.0</t>
         </is>
       </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Versão minor, mas só correções.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6494,6 +7640,11 @@
       <c r="D91" t="inlineStr">
         <is>
           <t>2026-09-27T01:55:27+00:00</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -6565,6 +7716,11 @@
           <t>2025-11-05T06:53:04+00:00</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -6610,6 +7766,11 @@
       <c r="D93" t="inlineStr">
         <is>
           <t>2026-02-23T11:40:49+00:00</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -6677,6 +7838,11 @@
       <c r="D94" t="inlineStr">
         <is>
           <t>2026-05-15T07:02:08+00:00</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -6726,6 +7892,11 @@
           <t>https://github.com/cinnyapp/cinny/compare/v4.11.1...v4.12.0</t>
         </is>
       </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Notas são de outra versão.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6746,6 +7917,11 @@
       <c r="D95" t="inlineStr">
         <is>
           <t>2026-08-01T12:03:06+00:00</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -6808,6 +7984,11 @@
       <c r="D96" t="inlineStr">
         <is>
           <t>2026-09-15T16:00:26+00:00</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
@@ -6872,6 +8053,11 @@
           <t>2026-06-23T23:54:14+00:00</t>
         </is>
       </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
           <t>Initial tagged release.</t>
@@ -6907,6 +8093,11 @@
       <c r="D98" t="inlineStr">
         <is>
           <t>2026-07-07T23:29:55+00:00</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -6971,6 +8162,11 @@
           <t>2026-08-10T15:41:10+00:00</t>
         </is>
       </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -7042,6 +8238,11 @@
           <t>2026-09-03T17:19:54+00:00</t>
         </is>
       </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -7091,6 +8292,11 @@
       <c r="D101" t="inlineStr">
         <is>
           <t>2026-09-05T21:19:41+00:00</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -7167,6 +8373,11 @@
           <t>2025-12-02T18:42:13+00:00</t>
         </is>
       </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
           <t>### Patch Changes
@@ -7213,6 +8424,11 @@
           <t>2025-12-02T18:42:55+00:00</t>
         </is>
       </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
           <t>### Patch Changes
@@ -7258,6 +8474,11 @@
           <t>2026-03-31T18:44:39+00:00</t>
         </is>
       </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
           <t>### Patch Changes
@@ -7303,6 +8524,11 @@
           <t>2026-07-28T18:14:21+00:00</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
           <t>### Patch Changes
@@ -7345,6 +8571,11 @@
       <c r="D106" t="inlineStr">
         <is>
           <t>2026-08-11T11:46:03+00:00</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -7390,6 +8621,11 @@
       <c r="D107" t="inlineStr">
         <is>
           <t>2025-10-06T19:27:49+00:00</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -7453,6 +8689,11 @@
           <t>2026-02-10T22:39:47+00:00</t>
         </is>
       </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -7499,6 +8740,11 @@
       <c r="D109" t="inlineStr">
         <is>
           <t>2026-05-03T09:23:23+00:00</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -7570,6 +8816,11 @@
           <t>2026-06-18T17:32:28+00:00</t>
         </is>
       </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
           <t>## [1.7.1](https://github.com/community-shaders/skyrim-community-shaders/compare/v1.7.0...v1.7.1) (2026-06-18)
@@ -7627,6 +8878,11 @@
       <c r="D111" t="inlineStr">
         <is>
           <t>2026-09-23T18:50:51+00:00</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -7697,6 +8953,11 @@
           <t>2026-02-06T19:51:00+00:00</t>
         </is>
       </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
           <t>### 🐛 Bug Fixes &amp; Optimizations
@@ -7755,6 +9016,11 @@
       <c r="D113" t="inlineStr">
         <is>
           <t>2026-03-04T21:49:37+00:00</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
@@ -7825,6 +9091,11 @@
           <t>2026-04-06T17:36:22+00:00</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
           <t>### ✨ New Features &amp; Improvements
@@ -7890,6 +9161,11 @@
       <c r="D115" t="inlineStr">
         <is>
           <t>2026-07-01T20:00:47+00:00</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
@@ -7963,6 +9239,11 @@
           <t>2026-09-22T18:45:03+00:00</t>
         </is>
       </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
           <t>### ⚠️ Potential Breaking Changes
@@ -8032,6 +9313,11 @@
           <t>2026-01-14T20:45:47+00:00</t>
         </is>
       </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
           <t>[Release](https://github.com/dotnet/core/releases/tag/v10.0.2)
@@ -8082,6 +9368,11 @@
           <t>https://github.com/dotnet/efcore/compare/v9.0.12...v10.0.2</t>
         </is>
       </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Anterior de outra linha de versão; julguei pelas notas.</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8102,6 +9393,11 @@
       <c r="D118" t="inlineStr">
         <is>
           <t>2026-04-14T20:59:12+00:00</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
@@ -8154,6 +9450,11 @@
           <t>https://github.com/dotnet/efcore/compare/v8.0.26...v9.0.15</t>
         </is>
       </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Anterior de outra linha de versão; julguei pelas notas.</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8174,6 +9475,11 @@
       <c r="D119" t="inlineStr">
         <is>
           <t>2026-05-12T18:41:16+00:00</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
@@ -8226,6 +9532,11 @@
           <t>https://github.com/dotnet/efcore/compare/v8.0.27...v9.0.16</t>
         </is>
       </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Anterior de outra linha de versão; julguei pelas notas.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8246,6 +9557,11 @@
       <c r="D120" t="inlineStr">
         <is>
           <t>2026-07-15T00:14:09+00:00</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
@@ -8298,6 +9614,11 @@
           <t>https://github.com/dotnet/efcore/compare/v8.0.29...v9.0.18</t>
         </is>
       </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Anterior de outra linha de versão; julguei pelas notas.</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8318,6 +9639,11 @@
       <c r="D121" t="inlineStr">
         <is>
           <t>2026-08-11T21:41:59+00:00</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -8370,6 +9696,11 @@
           <t>https://github.com/dotnet/efcore/compare/v9.0.19...v10.0.11</t>
         </is>
       </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Anterior de outra linha de versão; julguei pelas notas.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8390,6 +9721,11 @@
       <c r="D122" t="inlineStr">
         <is>
           <t>2026-01-30T07:38:49+00:00</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
@@ -8445,6 +9781,11 @@
       <c r="D123" t="inlineStr">
         <is>
           <t>2026-02-13T02:45:26+00:00</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
@@ -8513,6 +9854,11 @@
       <c r="D124" t="inlineStr">
         <is>
           <t>2026-04-29T03:00:59+00:00</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
@@ -8587,6 +9933,11 @@
           <t>2026-05-29T04:56:12+00:00</t>
         </is>
       </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
           <t>## Release 2026-05-22 V10.6.3
@@ -8633,6 +9984,11 @@
       <c r="D126" t="inlineStr">
         <is>
           <t>2026-05-31T06:22:27+00:00</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
@@ -8686,6 +10042,11 @@
       <c r="D127" t="inlineStr">
         <is>
           <t>2025-12-14T22:15:40+00:00</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
@@ -8756,6 +10117,11 @@
           <t>2025-12-14T22:34:08+00:00</t>
         </is>
       </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
           <t>## Version 4.1.1
@@ -8785,6 +10151,11 @@
           <t>https://github.com/dynamoose/dynamoose/compare/v4.1.0...v4.1.1</t>
         </is>
       </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Corrige o publish da versão anterior.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8805,6 +10176,11 @@
       <c r="D129" t="inlineStr">
         <is>
           <t>2025-12-14T23:00:51+00:00</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
@@ -8858,6 +10234,11 @@
           <t>2026-01-11T21:19:36+00:00</t>
         </is>
       </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
           <t>## Version 4.1.4
@@ -8909,6 +10290,11 @@
           <t>2026-01-11T21:45:00+00:00</t>
         </is>
       </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
           <t>## Version 4.1.5
@@ -8958,6 +10344,11 @@
       <c r="D132" t="inlineStr">
         <is>
           <t>2026-01-26T17:38:57+00:00</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
@@ -9030,6 +10421,11 @@
           <t>2026-02-09T20:58:40+00:00</t>
         </is>
       </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
           <t>&lt;!-- Release notes generated using configuration in .github/release.yaml at 2.50.0 --&gt;
@@ -9101,6 +10497,11 @@
           <t>2026-04-14T11:17:42+00:00</t>
         </is>
       </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
           <t>&lt;!-- Release notes generated using configuration in .github/release.yaml at 2.51.0 --&gt;
@@ -9171,6 +10572,11 @@
           <t>2026-09-09T20:42:41+00:00</t>
         </is>
       </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
           <t>&lt;!-- Release notes generated using configuration in .github/release.yaml at 2.53.0 --&gt;
@@ -9242,6 +10648,11 @@
           <t>2026-09-24T19:41:58+00:00</t>
         </is>
       </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
           <t>&lt;!-- Release notes generated using configuration in .github/release.yaml at 2.54.0 --&gt;
@@ -9306,6 +10717,11 @@
           <t>2026-07-01T18:33:51+00:00</t>
         </is>
       </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
           <t>Standalone RDE dashboard build for `hexclave dev` (version 1.0.43).</t>
@@ -9341,6 +10757,11 @@
       <c r="D138" t="inlineStr">
         <is>
           <t>2026-07-24T22:44:23+00:00</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
@@ -9389,6 +10810,11 @@
       <c r="D139" t="inlineStr">
         <is>
           <t>2026-07-25T23:59:37+00:00</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
@@ -9441,6 +10867,11 @@
           <t>2026-08-03T19:22:16+00:00</t>
         </is>
       </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
           <t>Standalone RDE dashboard build for `hexclave dev` (version 1.0.73).</t>
@@ -9483,6 +10914,11 @@
       <c r="D141" t="inlineStr">
         <is>
           <t>2026-08-03T22:39:27+00:00</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -9535,6 +10971,11 @@
       <c r="D142" t="inlineStr">
         <is>
           <t>2026-03-26T15:19:28+00:00</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
@@ -9577,6 +11018,11 @@
           <t>https://github.com/infinispan/infinispan/compare/5.1.8.Final...5.2.23.Final</t>
         </is>
       </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Anterior de outra linha de versão; julguei pelas notas.</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -9597,6 +11043,11 @@
       <c r="D143" t="inlineStr">
         <is>
           <t>2026-03-26T15:19:32+00:00</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -9639,6 +11090,11 @@
           <t>https://github.com/infinispan/infinispan/compare/7.0.3.Final...7.1.1.Final</t>
         </is>
       </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Anterior de outra linha de versão; julguei pelas notas.</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -9659,6 +11115,11 @@
       <c r="D144" t="inlineStr">
         <is>
           <t>2026-03-26T15:19:46+00:00</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
@@ -9701,6 +11162,11 @@
           <t>https://github.com/infinispan/infinispan/compare/12.0.2.Final...12.1.16.Final</t>
         </is>
       </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Anterior de outra linha de versão; julguei pelas notas.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9721,6 +11187,11 @@
       <c r="D145" t="inlineStr">
         <is>
           <t>2026-04-24T14:43:52+00:00</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
@@ -9794,6 +11265,11 @@
           <t>2026-06-08T07:15:08+00:00</t>
         </is>
       </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -9842,6 +11318,11 @@
           <t>https://github.com/infinispan/infinispan/compare/16.2.1...16.0.13</t>
         </is>
       </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Anterior de outra linha de versão; julguei pelas notas.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9862,6 +11343,11 @@
       <c r="D147" t="inlineStr">
         <is>
           <t>2025-12-08T21:12:38+00:00</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -9945,6 +11431,11 @@
           <t>2026-02-19T04:39:10+00:00</t>
         </is>
       </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
           <t>This release upgrades from Electron 33 to Electron 40, adds Linux sandboxing overhaul, and breaks apart install planning phase so that it doesn't block installing a game.
@@ -10015,6 +11506,11 @@
           <t>2026-05-18T19:46:13+00:00</t>
         </is>
       </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
           <t>A follow-up to 26.12.0 with Upload page fixes and an Electron bump.
@@ -10070,6 +11566,11 @@
       <c r="D150" t="inlineStr">
         <is>
           <t>2026-07-07T23:15:03+00:00</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
@@ -10128,6 +11629,11 @@
           <t>2026-08-03T03:24:25+00:00</t>
         </is>
       </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
           <t>This is a small patch to address crashing issue introduced in the last version on MacOS due to misconfigured entitlements.
@@ -10171,6 +11677,11 @@
       <c r="D152" t="inlineStr">
         <is>
           <t>2025-10-16T21:34:05+00:00</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -10240,6 +11751,11 @@
           <t>2025-12-04T10:51:59+00:00</t>
         </is>
       </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -10288,6 +11804,11 @@
       <c r="D154" t="inlineStr">
         <is>
           <t>2026-07-22T08:55:34+00:00</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
@@ -10364,6 +11885,11 @@
           <t>2026-09-09T11:35:06+00:00</t>
         </is>
       </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -10424,6 +11950,11 @@
           <t>2026-09-29T12:25:36+00:00</t>
         </is>
       </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -10475,6 +12006,11 @@
       <c r="D157" t="inlineStr">
         <is>
           <t>2025-10-30T07:14:00+00:00</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
@@ -10555,6 +12091,11 @@
           <t>2025-11-16T11:51:10+00:00</t>
         </is>
       </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
           <t>FluffyChat v2.3.0 fixes a possible database corruption bug on Android, also fixes a
@@ -10632,6 +12173,11 @@
           <t>2026-03-25T14:21:45+00:00</t>
         </is>
       </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
           <t>Full changelog: https://github.com/krille-chan/fluffychat/blob/main/CHANGELOG.md</t>
@@ -10694,6 +12240,11 @@
           <t>2026-08-17T10:54:05+00:00</t>
         </is>
       </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
           <t>Full changelog: https://github.com/krille-chan/fluffychat/blob/main/CHANGELOG.md</t>
@@ -10715,6 +12266,11 @@
           <t>https://github.com/krille-chan/fluffychat/compare/v2.9.0...v2.9.1</t>
         </is>
       </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Revert de feature.</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -10735,6 +12291,11 @@
       <c r="D161" t="inlineStr">
         <is>
           <t>2026-08-29T10:22:59+00:00</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
@@ -10760,6 +12321,11 @@
           <t>https://github.com/krille-chan/fluffychat/compare/v2.9.1...v2.9.4</t>
         </is>
       </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Hotfix.</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -10780,6 +12346,11 @@
       <c r="D162" t="inlineStr">
         <is>
           <t>2025-10-09T07:51:51+00:00</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
@@ -10854,6 +12425,11 @@
           <t>2025-10-09T09:04:30+00:00</t>
         </is>
       </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
           <t>Private Open AI Platform for Kubernetes.</t>
@@ -10896,6 +12472,11 @@
           <t>2025-12-03T11:50:47+00:00</t>
         </is>
       </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
           <t>A Helm chart for Kubernetes</t>
@@ -10936,6 +12517,11 @@
       <c r="D165" t="inlineStr">
         <is>
           <t>2026-07-30T09:53:07+00:00</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -10996,6 +12582,11 @@
           <t>2026-09-30T08:04:59+00:00</t>
         </is>
       </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
           <t>Private Open AI Platform for Kubernetes.</t>
@@ -11033,6 +12624,11 @@
       <c r="D167" t="inlineStr">
         <is>
           <t>2025-10-05T12:34:22+00:00</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
@@ -11095,6 +12691,11 @@
           <t>2025-11-30T10:25:32+00:00</t>
         </is>
       </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -11157,6 +12758,11 @@
           <t>2026-01-20T10:08:36+00:00</t>
         </is>
       </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -11210,6 +12816,11 @@
       <c r="D170" t="inlineStr">
         <is>
           <t>2026-07-09T14:04:18+00:00</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
@@ -11282,6 +12893,11 @@
           <t>2026-09-07T14:00:38+00:00</t>
         </is>
       </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -11330,6 +12946,11 @@
       <c r="D172" t="inlineStr">
         <is>
           <t>2025-10-23T21:23:37+00:00</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -11409,6 +13030,11 @@
           <t>2025-11-21T16:19:36+00:00</t>
         </is>
       </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
           <t>#### New Features
@@ -11477,6 +13103,11 @@
       <c r="D174" t="inlineStr">
         <is>
           <t>2026-02-17T18:37:11+00:00</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -11561,6 +13192,11 @@
           <t>2026-03-05T00:44:03+00:00</t>
         </is>
       </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
           <t>#### Compatibility
@@ -11606,6 +13242,11 @@
       <c r="D176" t="inlineStr">
         <is>
           <t>2026-06-03T14:23:23+00:00</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
@@ -11687,6 +13328,11 @@
           <t>2025-10-01T17:44:59+00:00</t>
         </is>
       </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
           <t>Below are some of the highlights for the 1.21 release of the QDK.
@@ -11766,6 +13412,11 @@
           <t>2025-12-09T17:23:38+00:00</t>
         </is>
       </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
           <t>Below are some of the highlights for the 1.23 release of the QDK.
@@ -11838,6 +13489,11 @@
           <t>2026-03-31T18:23:03+00:00</t>
         </is>
       </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
           <t>Below are some of the highlights for the 1.27 release of the QDK.
@@ -11910,6 +13566,11 @@
       <c r="D180" t="inlineStr">
         <is>
           <t>2026-07-30T23:02:53+00:00</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
@@ -12003,6 +13664,11 @@
           <t>2026-09-03T14:38:09+00:00</t>
         </is>
       </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
           <t>The 1.32 release of the QDK is packed with new features and capabilities, along with numerous bug fixes and performance improvements. Highlights include new interactive learning content for quantum chemistry, a Bloch sphere visualizer, QDK-Stim support, non-Clifford stabilizer simulation, the new Q# `parallel` keyword, improved circuit rendering, and more.
@@ -12069,6 +13735,11 @@
           <t>2025-10-02T09:17:33+00:00</t>
         </is>
       </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
           <t>Here is a list of changes since last release [1.1.0](https://github.com/mullvad/mullvadvpn-app/releases/tag/desktop%2Finstaller-downloader%2F1.1.0):
@@ -12133,6 +13804,11 @@
           <t>2025-12-09T10:01:17+00:00</t>
         </is>
       </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
           <t>This release is for desktop only.
@@ -12191,6 +13867,11 @@
           <t>https://github.com/mullvad/mullvadvpn-app/compare/android%2F2025.11...2025.14</t>
         </is>
       </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Anterior de outra linha de versão; julguei pelas notas.</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -12211,6 +13892,11 @@
       <c r="D184" t="inlineStr">
         <is>
           <t>2026-02-05T13:08:42+00:00</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
@@ -12268,6 +13954,11 @@
           <t>https://github.com/mullvad/mullvadvpn-app/compare/2025.14...android%2F2026.1</t>
         </is>
       </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Anterior de outra linha de versão; julguei pelas notas.</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -12288,6 +13979,11 @@
       <c r="D185" t="inlineStr">
         <is>
           <t>2026-04-27T12:17:09+00:00</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
@@ -12362,6 +14058,11 @@
       <c r="D186" t="inlineStr">
         <is>
           <t>2026-08-17T11:00:42+00:00</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
@@ -12424,6 +14125,11 @@
           <t>https://github.com/mullvad/mullvadvpn-app/compare/android%2F2026.8...2026.4</t>
         </is>
       </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Anterior de outra linha de versão; julguei pelas notas.</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -12444,6 +14150,11 @@
       <c r="D187" t="inlineStr">
         <is>
           <t>2025-10-05T15:15:18+00:00</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
@@ -12518,6 +14229,11 @@
           <t>2025-10-27T20:02:11+00:00</t>
         </is>
       </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -12580,6 +14296,11 @@
           <t>2025-12-17T19:32:26+00:00</t>
         </is>
       </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -12637,6 +14358,11 @@
       <c r="D190" t="inlineStr">
         <is>
           <t>2026-04-03T20:18:11+00:00</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
@@ -12711,6 +14437,11 @@
           <t>2026-07-04T06:58:14+00:00</t>
         </is>
       </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
           <t># What's Changed
@@ -12765,6 +14496,11 @@
       <c r="D192" t="inlineStr">
         <is>
           <t>2025-10-30T01:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
@@ -12836,6 +14572,11 @@
           <t>2026-02-04T16:02:19+00:00</t>
         </is>
       </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -12894,6 +14635,11 @@
           <t>2026-05-16T00:12:39+00:00</t>
         </is>
       </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -12948,6 +14694,11 @@
           <t>2026-08-10T21:15:01+00:00</t>
         </is>
       </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -12991,6 +14742,11 @@
       <c r="D196" t="inlineStr">
         <is>
           <t>2026-09-29T17:42:00+00:00</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
@@ -13052,6 +14808,11 @@
       <c r="D197" t="inlineStr">
         <is>
           <t>2025-10-29T17:15:43+00:00</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
@@ -13124,6 +14885,11 @@
           <t>2026-03-20T17:33:28+00:00</t>
         </is>
       </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
           <t>This release adds the following new features.
@@ -13193,6 +14959,11 @@
           <t>2026-04-10T19:10:21+00:00</t>
         </is>
       </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
           <t>This is a patch release containing the following bug fixes.
@@ -13238,6 +15009,11 @@
       <c r="D200" t="inlineStr">
         <is>
           <t>2026-08-19T17:44:53+00:00</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
@@ -13307,6 +15083,11 @@
           <t>2026-09-11T19:31:55+00:00</t>
         </is>
       </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
           <t>This is a patch release containing the following fixes.
@@ -13354,6 +15135,11 @@
       <c r="D202" t="inlineStr">
         <is>
           <t>2025-12-07T06:24:18+00:00</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
@@ -13423,6 +15209,11 @@
           <t>2026-01-03T14:17:12+00:00</t>
         </is>
       </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
           <t>## pH7 Social Dating Builder, v18.1 Release! ⚡️
@@ -13498,6 +15289,11 @@
           <t>2026-07-14T15:00:58+00:00</t>
         </is>
       </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
           <t>## pH7 Social Dating Builder, v18.4.1 Released!
@@ -13548,6 +15344,11 @@
       <c r="D205" t="inlineStr">
         <is>
           <t>2026-08-28T09:51:17+00:00</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
@@ -13629,6 +15430,11 @@
           <t>2026-09-22T12:44:27+00:00</t>
         </is>
       </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
           <t>**pH7 Social Dating Builder 19.3.0** is out, focusing on security, authentication, reliability, and PHP 8.2+ compatibility.
@@ -13693,6 +15499,11 @@
           <t>2026-08-13T20:02:52+00:00</t>
         </is>
       </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
           <t>## Changelog
@@ -13742,6 +15553,11 @@
           <t>2026-08-18T00:00:08+00:00</t>
         </is>
       </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
           <t>## Changelog
@@ -13785,6 +15601,11 @@
       <c r="D209" t="inlineStr">
         <is>
           <t>2026-08-18T05:03:33+00:00</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
@@ -13848,6 +15669,11 @@
           <t>2026-08-19T05:47:02+00:00</t>
         </is>
       </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
           <t>## Changelog
@@ -13905,6 +15731,11 @@
           <t>2026-08-31T19:25:19+00:00</t>
         </is>
       </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
           <t>## Changelog
@@ -13948,6 +15779,11 @@
       <c r="D212" t="inlineStr">
         <is>
           <t>2025-12-20T01:42:42+00:00</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
@@ -14021,6 +15857,11 @@
           <t>2025-12-22T17:28:02+00:00</t>
         </is>
       </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
           <t>Trigger re-build to produce libscalene.dll.</t>
@@ -14063,6 +15904,11 @@
       <c r="D214" t="inlineStr">
         <is>
           <t>2026-01-31T20:13:16+00:00</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
@@ -14115,6 +15961,11 @@
       <c r="D215" t="inlineStr">
         <is>
           <t>2026-03-22T15:30:23+00:00</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
@@ -14186,6 +16037,11 @@
           <t>2026-05-12T18:44:45+00:00</t>
         </is>
       </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -14261,6 +16117,11 @@
           <t>2025-10-14T15:02:11+00:00</t>
         </is>
       </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
           <t>[compare changes](https://github.com/qiutongxue/oba-live-tool/compare/v1.5.11...v1.5.12)
@@ -14336,6 +16197,11 @@
           <t>2025-11-05T15:39:40+00:00</t>
         </is>
       </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
           <t>[compare changes](https://github.com/qiutongxue/oba-live-tool/compare/v1.5.12...v1.5.13)
@@ -14389,6 +16255,11 @@
       <c r="D219" t="inlineStr">
         <is>
           <t>2025-12-04T16:28:09+00:00</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F219" s="3" t="inlineStr">
@@ -14454,6 +16325,11 @@
           <t>2026-03-19T09:05:35+00:00</t>
         </is>
       </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
           <t>[compare changes](https://github.com/qiutongxue/oba-live-tool/compare/v1.5.22...v1.5.23)
@@ -14507,6 +16383,11 @@
           <t>2026-09-11T18:58:36+00:00</t>
         </is>
       </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
           <t>## v1.6.2
@@ -14554,6 +16435,11 @@
       <c r="D222" t="inlineStr">
         <is>
           <t>2025-10-18T06:53:07+00:00</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr">
@@ -14615,6 +16501,11 @@
       <c r="D223" t="inlineStr">
         <is>
           <t>2025-12-11T05:07:45+00:00</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
@@ -14692,6 +16583,11 @@
           <t>2026-02-25T03:31:53+00:00</t>
         </is>
       </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -14740,6 +16636,11 @@
           <t>https://github.com/rachelos/we-mp-rss/compare/v1.4.8...v1.4.9</t>
         </is>
       </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Commits sem descrição útil.</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -14760,6 +16661,11 @@
       <c r="D225" t="inlineStr">
         <is>
           <t>2026-04-14T15:31:50+00:00</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
@@ -14810,6 +16716,11 @@
           <t>https://github.com/rachelos/we-mp-rss/compare/v1.5.0...v1.5.1</t>
         </is>
       </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>Commits sem descrição útil.</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -14830,6 +16741,11 @@
       <c r="D226" t="inlineStr">
         <is>
           <t>2026-04-16T05:35:26+00:00</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr">
@@ -14890,6 +16806,11 @@
           <t>2026-02-24T14:25:40+00:00</t>
         </is>
       </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
           <t>## What's New in v0.5.1
@@ -14933,6 +16854,11 @@
       <c r="D228" t="inlineStr">
         <is>
           <t>2026-04-19T08:31:28+00:00</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
@@ -15008,6 +16934,11 @@
           <t>2026-05-29T13:34:29+00:00</t>
         </is>
       </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
           <t>## Docker Quickstart
@@ -15077,6 +17008,11 @@
           <t>2026-07-14T13:30:49+00:00</t>
         </is>
       </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
           <t>## Docker Quickstart
@@ -15165,6 +17101,11 @@
           <t>2026-09-29T07:27:20+00:00</t>
         </is>
       </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
           <t>## Docker Quickstart
@@ -15237,6 +17178,11 @@
           <t>2025-12-20T13:38:04+00:00</t>
         </is>
       </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
           <t>7f8043a795cc6e98000d10894769c2aa53fc2b97 Upgrade dependencies (#1744)
@@ -15298,6 +17244,11 @@
           <t>2026-02-04T19:02:16+00:00</t>
         </is>
       </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
           <t>ae2bcbf8c5e2a90b8ee6342e08cb3002e2c18037 Upgrade dependencies (#1747)
@@ -15343,6 +17294,11 @@
           <t>2026-03-05T20:44:18+00:00</t>
         </is>
       </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
           <t>579b2b0f91ee174394ab7274958adde0bed048b5 Peer dependencies (#1751)
@@ -15386,6 +17342,11 @@
       <c r="D235" t="inlineStr">
         <is>
           <t>2026-08-17T19:21:15+00:00</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F235" s="3" t="inlineStr">
@@ -15447,6 +17408,11 @@
           <t>2026-08-31T20:04:30+00:00</t>
         </is>
       </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
           <t>311057e33c3ae4b2a915a383caea0647467f5315 Fix serving assets from paths containing dot directories (#1772)
@@ -15490,6 +17456,11 @@
       <c r="D237" t="inlineStr">
         <is>
           <t>2025-12-29T20:30:41+00:00</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr">
@@ -15546,6 +17517,11 @@
           <t>2026-02-09T12:15:44+00:00</t>
         </is>
       </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
           <t>## [2.33.6](https://github.com/remeda/remeda/compare/v2.33.5...v2.33.6) (2026-02-09)
@@ -15592,6 +17568,11 @@
       <c r="D239" t="inlineStr">
         <is>
           <t>2026-03-31T11:58:20+00:00</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F239" s="3" t="inlineStr">
@@ -15626,6 +17607,11 @@
           <t>https://github.com/remeda/remeda/compare/v2.33.6...v2.33.7</t>
         </is>
       </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>Diz 'fix', mas adiciona parâmetro.</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -15646,6 +17632,11 @@
       <c r="D240" t="inlineStr">
         <is>
           <t>2026-08-24T19:35:30+00:00</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
@@ -15670,6 +17661,11 @@
           <t>https://github.com/remeda/remeda/compare/v2.43.0...v2.44.0</t>
         </is>
       </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>Versão minor, mas só correção.</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -15690,6 +17686,11 @@
       <c r="D241" t="inlineStr">
         <is>
           <t>2026-09-09T17:15:01+00:00</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
@@ -15737,6 +17738,11 @@
       <c r="D242" t="inlineStr">
         <is>
           <t>2026-04-17T16:57:35+00:00</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
@@ -15790,6 +17796,11 @@
           <t>2026-06-18T20:08:09+00:00</t>
         </is>
       </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
           <t>Docker images published to GHCR:
@@ -15834,6 +17845,11 @@
           <t>2026-06-24T21:15:13+00:00</t>
         </is>
       </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
           <t>Docker images published to GHCR:
@@ -15878,6 +17894,11 @@
           <t>2026-07-10T17:07:38+00:00</t>
         </is>
       </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -15920,6 +17941,11 @@
       <c r="D246" t="inlineStr">
         <is>
           <t>2026-09-01T23:16:46+00:00</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr">
@@ -15966,6 +17992,11 @@
       <c r="D247" t="inlineStr">
         <is>
           <t>2025-10-22T17:36:12+00:00</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F247" s="3" t="inlineStr">
@@ -16037,6 +18068,11 @@
           <t>2026-02-26T17:59:09+00:00</t>
         </is>
       </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
           <t>## [1.15.1](https://github.com/runfinch/finch/compare/v1.15.0...v1.15.1) (2026-02-26)
@@ -16081,6 +18117,11 @@
       <c r="D249" t="inlineStr">
         <is>
           <t>2026-05-29T17:22:59+00:00</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
@@ -16134,6 +18175,11 @@
       <c r="D250" t="inlineStr">
         <is>
           <t>2026-06-30T16:19:20+00:00</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr">
@@ -16198,6 +18244,11 @@
           <t>2026-08-20T22:48:38+00:00</t>
         </is>
       </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
           <t>## [1.18.0](https://github.com/runfinch/finch/compare/v1.17.2...v1.18.0) (2026-08-20)
@@ -16256,6 +18307,11 @@
           <t>2025-10-31T17:24:09+00:00</t>
         </is>
       </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
           <t>To install Sass 1.93.3, download one of the packages below and [add it to your PATH][], or see [the Sass website][] for full installation instructions.
@@ -16306,6 +18362,11 @@
           <t>2025-12-16T06:46:31+00:00</t>
         </is>
       </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
           <t>To install Sass 1.97.0, download one of the packages below and [add it to your PATH][], or see [the Sass website][] for full installation instructions.
@@ -16353,6 +18414,11 @@
           <t>2025-12-19T21:42:46+00:00</t>
         </is>
       </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
           <t>To install Sass 1.97.1, download one of the packages below and [add it to your PATH][], or see [the Sass website][] for full installation instructions.
@@ -16401,6 +18467,11 @@
           <t>2026-07-25T00:19:44+00:00</t>
         </is>
       </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
           <t>To install Sass 1.102.0, download one of the packages below and [add it to your PATH][], or see [the Sass website][] for full installation instructions.
@@ -16446,6 +18517,11 @@
       <c r="D256" t="inlineStr">
         <is>
           <t>2026-09-12T07:49:38+00:00</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr">
@@ -16512,6 +18588,11 @@
           <t>2025-10-03T18:45:51+00:00</t>
         </is>
       </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
           <t>&lt;!-- Release notes generated using configuration in .github/release.yml at master --&gt;
@@ -16568,6 +18649,11 @@
       <c r="D258" t="inlineStr">
         <is>
           <t>2026-03-15T00:24:48+00:00</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr">
@@ -16642,6 +18728,11 @@
           <t>2026-03-16T00:57:39+00:00</t>
         </is>
       </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
           <t>`2.6.1` is a patch release focused on restoring linked discussion thread creation when
@@ -16689,6 +18780,11 @@
       <c r="D260" t="inlineStr">
         <is>
           <t>2026-04-12T04:46:49+00:00</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr">
@@ -16740,6 +18836,11 @@
       <c r="D261" t="inlineStr">
         <is>
           <t>2026-07-13T14:30:35+00:00</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F261" s="3" t="inlineStr">
@@ -16811,6 +18912,11 @@
           <t>2025-10-28T11:25:16+00:00</t>
         </is>
       </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
           <t>## What’s Changed
@@ -16880,6 +18986,11 @@
           <t>2026-02-19T17:00:12+00:00</t>
         </is>
       </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -16936,6 +19047,11 @@
           <t>2026-04-20T17:21:08+00:00</t>
         </is>
       </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -16981,6 +19097,11 @@
       <c r="D265" t="inlineStr">
         <is>
           <t>2026-05-29T18:50:02+00:00</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F265" s="3" t="inlineStr">
@@ -17062,6 +19183,11 @@
           <t>2026-07-08T11:05:21+00:00</t>
         </is>
       </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -17140,6 +19266,11 @@
           <t>2025-10-14T13:54:13+00:00</t>
         </is>
       </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
           <t>### Added
@@ -17208,6 +19339,11 @@
           <t>2025-10-17T14:50:58+00:00</t>
         </is>
       </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
           <t>### Fixed
@@ -17253,6 +19389,11 @@
       <c r="D269" t="inlineStr">
         <is>
           <t>2025-12-01T15:40:35+00:00</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F269" s="3" t="inlineStr">
@@ -17304,6 +19445,11 @@
           <t>2026-04-27T13:54:30+00:00</t>
         </is>
       </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
           <t>Same as v0.7.2, since v0.7.3 contained breaking changes.</t>
@@ -17322,6 +19468,11 @@
       <c r="I270" s="2" t="inlineStr">
         <is>
           <t>https://github.com/tailwindlabs/prettier-plugin-tailwindcss/compare/v0.7.3...v0.7.4</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>Reverte a 0.7.3.</t>
         </is>
       </c>
     </row>
@@ -17344,6 +19495,11 @@
       <c r="D271" t="inlineStr">
         <is>
           <t>2026-04-27T13:56:48+00:00</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F271" s="3" t="inlineStr">
@@ -17419,6 +19575,11 @@
           <t>2025-12-21T07:11:38+00:00</t>
         </is>
       </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
           <t>### Changed
@@ -17485,6 +19646,11 @@
           <t>2026-04-06T14:05:41+00:00</t>
         </is>
       </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
           <t>### Added
@@ -17554,6 +19720,11 @@
           <t>2026-05-10T07:16:14+00:00</t>
         </is>
       </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
           <t>### Changed
@@ -17604,6 +19775,11 @@
       <c r="D275" t="inlineStr">
         <is>
           <t>2026-07-19T16:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F275" s="3" t="inlineStr">
@@ -17679,6 +19855,11 @@
           <t>2026-07-25T05:03:10+00:00</t>
         </is>
       </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
           <t>### Fixed
@@ -17723,6 +19904,11 @@
       <c r="D277" t="inlineStr">
         <is>
           <t>2026-01-23T13:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F277" s="3" t="inlineStr">
@@ -17795,6 +19981,11 @@
           <t>2026-02-23T03:14:41+00:00</t>
         </is>
       </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
           <t>### ⛰️  Features
@@ -17861,6 +20052,11 @@
           <t>2026-04-12T00:58:17+00:00</t>
         </is>
       </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
           <t>### ⛰️  Features
@@ -17917,6 +20113,11 @@
       <c r="D280" t="inlineStr">
         <is>
           <t>2026-07-11T07:50:15+00:00</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
@@ -17989,6 +20190,11 @@
           <t>2026-07-18T00:47:46+00:00</t>
         </is>
       </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
           <t>## [0.6.2](https://github.com/vicanso/zedis/compare/v0.5.4..v0.6.2) - 2026-07-18
@@ -18059,6 +20265,11 @@
           <t>2025-12-04T01:04:33+00:00</t>
         </is>
       </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
           <t>**Full Changelog**: https://github.com/vue-stripe/vue-stripe/compare/v4.5.0...v5.0.0
@@ -18109,6 +20320,11 @@
       <c r="D283" t="inlineStr">
         <is>
           <t>2025-12-04T18:44:44+00:00</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F283" s="3" t="inlineStr">
@@ -18175,6 +20391,11 @@
           <t>2025-12-08T13:57:02+00:00</t>
         </is>
       </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
           <t>**Full Changelog**: https://github.com/vue-stripe/vue-stripe/compare/v5.2.0...v5.2.1</t>
@@ -18233,6 +20454,11 @@
       <c r="D285" t="inlineStr">
         <is>
           <t>2026-06-18T05:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F285" s="3" t="inlineStr">
@@ -18306,6 +20532,11 @@
           <t>2026-06-20T16:27:13+00:00</t>
         </is>
       </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -18355,6 +20586,11 @@
       <c r="D287" t="inlineStr">
         <is>
           <t>2026-07-18T16:03:57+00:00</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F287" s="3" t="inlineStr">
@@ -18413,6 +20649,11 @@
       <c r="D288" t="inlineStr">
         <is>
           <t>2026-07-18T18:16:33+00:00</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr">
@@ -18467,6 +20708,11 @@
       <c r="D289" t="inlineStr">
         <is>
           <t>2026-08-03T17:58:53+00:00</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F289" s="3" t="inlineStr">
@@ -18525,6 +20771,11 @@
           <t>2026-08-08T17:48:53+00:00</t>
         </is>
       </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
           <t># CyberCode v1.1.20
@@ -18576,6 +20827,11 @@
       <c r="D291" t="inlineStr">
         <is>
           <t>2026-08-08T18:24:01+00:00</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F291" s="3" t="inlineStr">
@@ -18612,6 +20868,11 @@
           <t>https://github.com/wk42worldworld/cybercode/compare/v1.1.20...v1.1.21</t>
         </is>
       </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>Diz 'fix', mas é feature.</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -18632,6 +20893,11 @@
       <c r="D292" t="inlineStr">
         <is>
           <t>2025-10-11T01:52:22+00:00</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr">
@@ -18679,6 +20945,11 @@
       <c r="D293" t="inlineStr">
         <is>
           <t>2026-04-05T15:09:05+00:00</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F293" s="3" t="inlineStr">
@@ -18739,6 +21010,11 @@
           <t>2026-05-30T12:11:47+00:00</t>
         </is>
       </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
           <t>## Changes in v2.1.17
@@ -18796,6 +21072,11 @@
           <t>2026-07-10T15:18:07+00:00</t>
         </is>
       </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
           <t>## Changes in v2.1.32
@@ -18846,6 +21127,11 @@
       <c r="D296" t="inlineStr">
         <is>
           <t>2026-08-16T06:04:22+00:00</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>sim</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr">
@@ -18915,6 +21201,11 @@
       <c r="D297" t="inlineStr">
         <is>
           <t>2025-10-20T03:21:31+00:00</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F297" s="3" t="inlineStr">
@@ -18987,6 +21278,11 @@
           <t>2026-01-31T00:17:32+00:00</t>
         </is>
       </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
       <c r="F298" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -19056,6 +21352,11 @@
           <t>2026-04-09T08:24:07+00:00</t>
         </is>
       </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
       <c r="F299" s="3" t="inlineStr">
         <is>
           <t>## What's Changed
@@ -19116,6 +21417,11 @@
       <c r="D300" t="inlineStr">
         <is>
           <t>2026-06-23T23:56:00+00:00</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr">
@@ -19188,6 +21494,11 @@
       <c r="D301" t="inlineStr">
         <is>
           <t>2026-07-09T05:45:02+00:00</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>não</t>
         </is>
       </c>
       <c r="F301" s="3" t="inlineStr">
